--- a/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/LogicalModel/OrganspezifischeZusatzmodule</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-lm-onko-organspezifische-zusatzmodule</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,7 @@
     <t>Mapping: Organspezifische Zusatzmodule LogicalModel oBDS Mapping</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule</t>
   </si>
   <si>
     <t/>
@@ -264,7 +264,7 @@
 </t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.id</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.id</t>
   </si>
   <si>
     <t>1</t>
@@ -283,7 +283,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.extension</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.extension</t>
   </si>
   <si>
     <t>extensions
@@ -320,7 +320,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -339,13 +339,13 @@
     <t>Modul Mamma (M1–M8)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.modifierExtension</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -368,7 +368,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.Menopausenstatus</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.Menopausenstatus</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -387,7 +387,7 @@
     <t>M1</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen</t>
   </si>
   <si>
     <t>Rezeptorstatus Estrogen</t>
@@ -402,16 +402,16 @@
     <t>M2</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.Status</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.Status</t>
   </si>
   <si>
     <t>Estrogen-Rezeptorstatus</t>
@@ -423,7 +423,7 @@
     <t>Observation.valueCodeableConcept</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.AnteilPositiveZellen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.AnteilPositiveZellen</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity
@@ -442,7 +442,7 @@
     <t>M2 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusEstrogen.Faerbeintensitaet</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusEstrogen.Faerbeintensitaet</t>
   </si>
   <si>
     <t>Färbeintensität</t>
@@ -454,7 +454,7 @@
     <t>Observation.component.where(code.coding.system='http://snomed.info/sct' and code.coding.code='1236874005').valueCodeableConcept</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron</t>
   </si>
   <si>
     <t>Rezeptorstatus Progesteron</t>
@@ -469,16 +469,16 @@
     <t>M3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.Status</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.Status</t>
   </si>
   <si>
     <t>Progesteron-Rezeptorstatus</t>
@@ -487,7 +487,7 @@
     <t>Kategoriale Bewertung des Progesteron-Rezeptorstatus: positiv/negativ. oBDS M3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.AnteilPositiveZellen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.AnteilPositiveZellen</t>
   </si>
   <si>
     <t>Quantitative Bestimmung in Prozent. Komponente zu oBDS M3 (keine eigene Feldnummer, S3-Leitlinie).</t>
@@ -499,7 +499,7 @@
     <t>M3 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.RezeptorstatusProgesteron.Faerbeintensitaet</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.RezeptorstatusProgesteron.Faerbeintensitaet</t>
   </si>
   <si>
     <t>Qualitative Bewertung der Färbeintensität. Komponente zu oBDS M3 (keine eigene Feldnummer, S3-Leitlinie).</t>
@@ -508,7 +508,7 @@
     <t>Observation.component.where(code.coding.system='http://snomed.info/sct' and code.coding.code='1237278006').valueCodeableConcept</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.StatusHer2neu</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.StatusHer2neu</t>
   </si>
   <si>
     <t>Her2neu-Status</t>
@@ -523,7 +523,7 @@
     <t>M4</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.PraeoperativeMarkierung</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.PraeoperativeMarkierung</t>
   </si>
   <si>
     <t>Präoperative Markierung</t>
@@ -538,16 +538,16 @@
     <t>M5</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.PraeoperativeMarkierung.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.PraeoperativeMarkierung.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.PraeoperativeMarkierung.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.PraeoperativeMarkierung.Modalitaet</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.PraeoperativeMarkierung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.PraeoperativeMarkierung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.PraeoperativeMarkierung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.PraeoperativeMarkierung.Modalitaet</t>
   </si>
   <si>
     <t>Markierungsmodalität</t>
@@ -562,7 +562,7 @@
     <t>M5 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation</t>
   </si>
   <si>
     <t>Mamma-Operation</t>
@@ -577,16 +577,16 @@
     <t>kein oBDS-Modulfeld</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation.Operationstyp</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation.Operationstyp</t>
   </si>
   <si>
     <t>Operationstyp</t>
@@ -598,7 +598,7 @@
     <t>Procedure.code</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.MammaOperation.IntraoperativesImaging</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.MammaOperation.IntraoperativesImaging</t>
   </si>
   <si>
     <t>Intraoperatives Präparatröntgen/Sonografie</t>
@@ -613,7 +613,7 @@
     <t>M6</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.TumorgroesseInvasiv</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.TumorgroesseInvasiv</t>
   </si>
   <si>
     <t>Tumorgröße invasives Karzinom</t>
@@ -628,7 +628,7 @@
     <t>M7</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Mamma.TumorgroesseDCIS</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Mamma.TumorgroesseDCIS</t>
   </si>
   <si>
     <t>Tumorgröße DCIS</t>
@@ -640,7 +640,7 @@
     <t>M8</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom</t>
   </si>
   <si>
     <t>Kolorektales Karzinom</t>
@@ -655,16 +655,16 @@
     <t>Modul Kolorektales Karzinom (KR1–KR10)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.TumorLokalisation</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.TumorLokalisation</t>
   </si>
   <si>
     <t>Tumor Lokalisation</t>
@@ -676,16 +676,16 @@
     <t>KR1</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.TumorLokalisation.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.TumorLokalisation.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.TumorLokalisation.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.TumorLokalisation.AbstandAnokutanlinie</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.TumorLokalisation.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.TumorLokalisation.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.TumorLokalisation.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.TumorLokalisation.AbstandAnokutanlinie</t>
   </si>
   <si>
     <t>Abstand Anokutanlinie</t>
@@ -697,7 +697,7 @@
     <t>Observation.where(code.coding.system='http://loinc.org' and code.coding.code='33748-5').valueQuantity</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren</t>
   </si>
   <si>
     <t>Bildgebende Verfahren</t>
@@ -709,16 +709,16 @@
     <t>KR5</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale</t>
   </si>
   <si>
     <t>MRT/CT Mesorektale Faszie</t>
@@ -730,16 +730,16 @@
     <t>Observation.where(code.coding.system='https://radelement.org' and code.coding.code='RDE96')</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.AbstandMesorektale</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.AbstandMesorektale</t>
   </si>
   <si>
     <t>Abstand Mesorektale Faszie</t>
@@ -751,7 +751,7 @@
     <t>Observation.valueQuantity</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.AbstandNichtVerfuegbarGrund</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.BildgebendeVerfahren.MRTMesorektale.AbstandNichtVerfuegbarGrund</t>
   </si>
   <si>
     <t>Grund für fehlende Abstandsmessung</t>
@@ -763,7 +763,7 @@
     <t>KR5 (Statusangabe)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation</t>
   </si>
   <si>
     <t>KRK Operation</t>
@@ -775,16 +775,16 @@
     <t>KR6, KR7, KR9</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.Operationstyp</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.Operationstyp</t>
   </si>
   <si>
     <t>Art des Eingriffs</t>
@@ -796,7 +796,7 @@
     <t>KR6</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.ASAKlassifikation</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.ASAKlassifikation</t>
   </si>
   <si>
     <t>ASA-Klassifikation</t>
@@ -811,7 +811,7 @@
     <t>KR9</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung</t>
   </si>
   <si>
     <t>Stoma Markierung</t>
@@ -826,16 +826,16 @@
     <t>KR7</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.Status</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.Status</t>
   </si>
   <si>
     <t>Markierungsstatus</t>
@@ -847,7 +847,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.StatusGrund</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.Operation.StomaMarkierung.StatusGrund</t>
   </si>
   <si>
     <t>Status Grund</t>
@@ -862,7 +862,7 @@
     <t>KR7 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung</t>
   </si>
   <si>
     <t>Pathologische Bewertung</t>
@@ -874,16 +874,16 @@
     <t>KR2–KR4, KR10</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.ResektionsraenderAboral</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.ResektionsraenderAboral</t>
   </si>
   <si>
     <t>Resektionsrand aboral</t>
@@ -898,7 +898,7 @@
     <t>KR2</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.ResektionsraenderCircumferell</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.ResektionsraenderCircumferell</t>
   </si>
   <si>
     <t>Resektionsrand circumferell</t>
@@ -913,7 +913,7 @@
     <t>KR3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.TMEQualitaet</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.TMEQualitaet</t>
   </si>
   <si>
     <t>TME Qualität</t>
@@ -928,7 +928,7 @@
     <t>KR4</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PathologischeBewertung.RASMutation</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PathologischeBewertung.RASMutation</t>
   </si>
   <si>
     <t>RAS-Mutation</t>
@@ -943,7 +943,7 @@
     <t>KR10</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen</t>
   </si>
   <si>
     <t>Postoperative Komplikationen</t>
@@ -955,16 +955,16 @@
     <t>KR8</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.Anastomoseninsuffizienz</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.KolorektalesKarzinom.PostoperativeKomplikationen.Anastomoseninsuffizienz</t>
   </si>
   <si>
     <t>Anastomoseninsuffizienz</t>
@@ -976,7 +976,7 @@
     <t>Observation.where(code.coding.system='http://snomed.info/sct' and code.coding.code='361317002').valueCodeableConcept</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata</t>
   </si>
   <si>
     <t>Prostata</t>
@@ -991,16 +991,16 @@
     <t>Modul Prostata (P1–P9)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore</t>
   </si>
   <si>
     <t>Gleason Score</t>
@@ -1015,22 +1015,22 @@
     <t>P1</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore.Score</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore.Score</t>
   </si>
   <si>
     <t>Summe aus primärem und sekundärem Pattern. oBDS P1</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonScore.GradeGroup</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonScore.GradeGroup</t>
   </si>
   <si>
     <t>Grade Group</t>
@@ -1045,7 +1045,7 @@
     <t>P1 (abgeleitet)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern</t>
   </si>
   <si>
     <t>Gleason Pattern</t>
@@ -1060,16 +1060,16 @@
     <t>P1 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern.PatternTyp</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern.PatternTyp</t>
   </si>
   <si>
     <t>Pattern Typ</t>
@@ -1081,7 +1081,7 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.GleasonPattern.PatternWert</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.GleasonPattern.PatternWert</t>
   </si>
   <si>
     <t>Pattern Wert</t>
@@ -1090,7 +1090,7 @@
     <t>Gleason Pattern Wert (1-5, ab 3 als maligne).</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.AnlassGleasonScore</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.AnlassGleasonScore</t>
   </si>
   <si>
     <t>Anlass Gleason-Score</t>
@@ -1105,7 +1105,7 @@
     <t>P2</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse</t>
   </si>
   <si>
     <t>Biopsie Ergebnisse</t>
@@ -1120,16 +1120,16 @@
     <t>P3–P6</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.DatumStanzen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.DatumStanzen</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -1148,7 +1148,7 @@
     <t>P3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.AnzahlStanzen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.AnzahlStanzen</t>
   </si>
   <si>
     <t>Anzahl Stanzen</t>
@@ -1163,7 +1163,7 @@
     <t>P4</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.AnzahlPositiverStanzen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.AnzahlPositiverStanzen</t>
   </si>
   <si>
     <t>Anzahl positive Stanzen</t>
@@ -1178,7 +1178,7 @@
     <t>P5</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.BiopsieErgebnisse.KarzinomBefallStanze</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.BiopsieErgebnisse.KarzinomBefallStanze</t>
   </si>
   <si>
     <t>Karzinom-Befall je Stanze</t>
@@ -1193,7 +1193,7 @@
     <t>P6</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.PSAWert</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.PSAWert</t>
   </si>
   <si>
     <t>PSA-Wert</t>
@@ -1208,7 +1208,7 @@
     <t>P7</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.DatumPSA</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.DatumPSA</t>
   </si>
   <si>
     <t>Datum PSA-Wert</t>
@@ -1223,7 +1223,7 @@
     <t>P8</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen</t>
   </si>
   <si>
     <t>Chirurgische Komplikationen</t>
@@ -1238,16 +1238,16 @@
     <t>P9</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen.ClavienDindoGrad</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen.ClavienDindoGrad</t>
   </si>
   <si>
     <t>Clavien-Dindo Grad</t>
@@ -1256,7 +1256,7 @@
     <t>Graduierung postoperativer Komplikationen nach Clavien-Dindo. oBDS P9</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.Prostata.ChirurgischeKomplikationen.KomplikationsArt</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.Prostata.ChirurgischeKomplikationen.KomplikationsArt</t>
   </si>
   <si>
     <t>Komplikationsart</t>
@@ -1271,7 +1271,7 @@
     <t>P9 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom</t>
   </si>
   <si>
     <t>Malignes Melanom</t>
@@ -1286,16 +1286,16 @@
     <t>Modul Malignes Melanom (MM1–MM4)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.Sicherheitsabstand</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.Sicherheitsabstand</t>
   </si>
   <si>
     <t>Sicherheitsabstand Primärtumor</t>
@@ -1310,7 +1310,7 @@
     <t>MM1</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.BreslowTiefe</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.BreslowTiefe</t>
   </si>
   <si>
     <t>Tumordicke (Breslow)</t>
@@ -1325,7 +1325,7 @@
     <t>MM2</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH</t>
   </si>
   <si>
     <t>Laktatdehydrogenase</t>
@@ -1340,16 +1340,16 @@
     <t>MM3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH.Wert</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH.Wert</t>
   </si>
   <si>
     <t>LDH-Wert</t>
@@ -1358,7 +1358,7 @@
     <t>Laktatdehydrogenase Aktivität in U/L als prognostischer Marker. oBDS MM3</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.LDH.Bewertung</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.LDH.Bewertung</t>
   </si>
   <si>
     <t>LDH-Bewertung</t>
@@ -1373,7 +1373,7 @@
     <t>MM3 (Komponente)</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.MalignesMelanom.Ulzeration</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.MalignesMelanom.Ulzeration</t>
   </si>
   <si>
     <t>Ulzeration</t>
@@ -1388,7 +1388,7 @@
     <t>MM4</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein</t>
   </si>
   <si>
     <t>Modul Allgemein</t>
@@ -1400,16 +1400,16 @@
     <t>Organübergreifende Ressourcen</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.id</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.extension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.modifierExtension</t>
-  </si>
-  <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.Sozialdienstkontakt</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.id</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.Sozialdienstkontakt</t>
   </si>
   <si>
     <t>Datum des Sozialdienstkontaktes</t>
@@ -1424,7 +1424,7 @@
     <t>M9 / KR11</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.Psychoonkologiekontakt</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.Psychoonkologiekontakt</t>
   </si>
   <si>
     <t>Datum des Psychoonkologiekontaktes</t>
@@ -1439,7 +1439,7 @@
     <t>Modul_Allgemein</t>
   </si>
   <si>
-    <t>OrganspezifischeZusatzmodule.ModulAllgemein.Studienteilnahme</t>
+    <t>mii-lm-onko-organspezifische-zusatzmodule.ModulAllgemein.Studienteilnahme</t>
   </si>
   <si>
     <t>Datum der Studienrekrutierung</t>
@@ -1758,8 +1758,8 @@
   <dimension ref="A1:AL134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="99.59375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="99.59375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="109.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="109.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1789,7 +1789,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="99.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="109.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-onko-organspezifische-zusatzmodule.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
